--- a/03_Learning_Management/00_Excel_Export/notes.xlsx
+++ b/03_Learning_Management/00_Excel_Export/notes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,23 +413,42 @@
         <v>Pinned</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
+        <v>Video Download Websites</v>
+      </c>
+      <c r="B2" t="str" xml:space="preserve">
+        <v xml:space="preserve">https://ssyou.online/en1423SK/
+https://en1.savefrom.net/1-youtube-video-downloader-18Cs/
+https://vidssave.com/youtube-video-downloader-3cx
+https://ssyoutube.online/en2/
+https://www.socialplug.io/free-tools/youtube-video-downloader
+https://ssyoutube.com/en803AM/</v>
+      </c>
+      <c r="C2" t="str">
+        <v>General</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Download Videos</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Dowload All Videos which are not in series</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
         <v>WebDev</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D3" t="str">
         <v>Yes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>